--- a/Halka_Arz_Verileri.xlsx
+++ b/Halka_Arz_Verileri.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Hazırlanıyor...</t>
+          <t>17 Eylül 2026</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
